--- a/Employee_Reports_wi52/Mohamed Faizal Mohamed Uvais Q0493.xlsx
+++ b/Employee_Reports_wi52/Mohamed Faizal Mohamed Uvais Q0493.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-321</v>
+        <v>-329</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-137</v>
+        <v>-145</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-137</v>
+        <v>-145</v>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -1460,11 +1460,11 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>-25</v>
+        <v>-33</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1509,11 +1509,11 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-25</v>
+        <v>-33</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1558,11 +1558,11 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-25</v>
+        <v>-33</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1607,11 +1607,11 @@
         </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -1656,11 +1656,11 @@
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
@@ -1671,41 +1671,41 @@
       <c r="K25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>IS0 55001 (Other Trainings)</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr"/>
-      <c r="D26" s="4" t="inlineStr"/>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>26-Aug-2024</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>26-Aug-2026</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr"/>
+      <c r="C26" s="3" t="inlineStr"/>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>24-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>23-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>726</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -1730,11 +1730,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7907</v>
+        <v>7899</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7902</v>
+        <v>7894</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7902</v>
+        <v>7894</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7899</v>
+        <v>7891</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7899</v>
+        <v>7891</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7899</v>
+        <v>7891</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7902</v>
+        <v>7894</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7908</v>
+        <v>7900</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
